--- a/connection/Data Api Berubah.xlsx
+++ b/connection/Data Api Berubah.xlsx
@@ -154,10 +154,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -470,11 +470,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -485,7 +485,7 @@
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
@@ -573,7 +573,7 @@
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>12</v>
       </c>
       <c r="C16" t="s">

--- a/connection/Data Api Berubah.xlsx
+++ b/connection/Data Api Berubah.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="60" windowWidth="20400" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="60" windowWidth="20400" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Perubahan Kelas Lengkap" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Report Grou and Dashboard" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
   <si>
     <t>API Nomor</t>
   </si>
@@ -85,13 +85,68 @@
   </si>
   <si>
     <t>vw_report_umsiswa</t>
+  </si>
+  <si>
+    <t>Report Group Uang Masuk &amp; Keluar</t>
+  </si>
+  <si>
+    <t>Api baru</t>
+  </si>
+  <si>
+    <t>Report Uang Masuk</t>
+  </si>
+  <si>
+    <t>Report Uang Keluar</t>
+  </si>
+  <si>
+    <t>Report Uang Masuk Keluar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modif vw_report_spp </t>
+  </si>
+  <si>
+    <t>Modif vw_report_ppdb</t>
+  </si>
+  <si>
+    <t>Modif vw_report_umlain</t>
+  </si>
+  <si>
+    <t>Modif vw_report_umsiswa</t>
+  </si>
+  <si>
+    <t>Modif vw_report_umsiswa_dll</t>
+  </si>
+  <si>
+    <t>Modif vw_report_act</t>
+  </si>
+  <si>
+    <t>Modif vw_report_pra_act</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">vw_report_uksiswa_dll </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(View baru)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +158,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -143,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -155,6 +218,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -470,11 +536,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
@@ -485,7 +551,7 @@
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
@@ -632,10 +698,122 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="B2:D19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="13.625" customWidth="1"/>
+    <col min="3" max="3" width="30.75" customWidth="1"/>
+    <col min="4" max="4" width="51.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="4">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="4">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
